--- a/Rain-Proposal-Tool/Engineering Knowledge Base.xlsx
+++ b/Rain-Proposal-Tool/Engineering Knowledge Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebb6c030e751b8a0/Documents/GitHub/Rain-Proposal-Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{A7A6ECBC-5FC6-4D0B-BC09-6EC3CF525B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53AE7744-C330-403F-9A3A-5123B46D3F8F}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{A7A6ECBC-5FC6-4D0B-BC09-6EC3CF525B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC1D7194-7950-4D86-B695-4094517891EC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{515DC161-E711-4AEE-AA3C-2BE043A01E76}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="64">
   <si>
     <t>Engineering Disciplines</t>
   </si>
@@ -135,6 +135,102 @@
   </si>
   <si>
     <t>Existing models available</t>
+  </si>
+  <si>
+    <t>Stormwater Management Strategy</t>
+  </si>
+  <si>
+    <t>overall drainage</t>
+  </si>
+  <si>
+    <t>peak flows</t>
+  </si>
+  <si>
+    <t>runoff</t>
+  </si>
+  <si>
+    <t>Climate change</t>
+  </si>
+  <si>
+    <t>pollutant</t>
+  </si>
+  <si>
+    <t>treatment</t>
+  </si>
+  <si>
+    <t>stormwater quality</t>
+  </si>
+  <si>
+    <t>waterway</t>
+  </si>
+  <si>
+    <t>Hydrological RORB model</t>
+  </si>
+  <si>
+    <t>Storage size</t>
+  </si>
+  <si>
+    <t>Flows</t>
+  </si>
+  <si>
+    <t>wetlands</t>
+  </si>
+  <si>
+    <t>sediment</t>
+  </si>
+  <si>
+    <t>Stormwater Management Plan</t>
+  </si>
+  <si>
+    <t>MUSIC</t>
+  </si>
+  <si>
+    <t>MUSIC models</t>
+  </si>
+  <si>
+    <t>stormwater quality outcomes</t>
+  </si>
+  <si>
+    <t>Communication with the authorities will be via phone and email. Additional meetings, workshops or authority meetings will be charged at hourly rates</t>
+  </si>
+  <si>
+    <t>No guarantees are made in any way that a favourable outcome will be achievable for the site.</t>
+  </si>
+  <si>
+    <t>We reserve the right to amend this proposal depending on any requirements obtained from Council and the CMA.</t>
+  </si>
+  <si>
+    <t>No flow or rainfall gauging is included.</t>
+  </si>
+  <si>
+    <t>It is assumed that the existing RORB model is fit for use and can be adopted as is. No fees are allowed for improving or fixing errors within the existing model.</t>
+  </si>
+  <si>
+    <t>ANCOLD Hydrology/assessment is excluded from this proposal, however can be undertaken at hourly rates if required;</t>
+  </si>
+  <si>
+    <t>Client and authority comments will be provided in a consolidated manner.</t>
+  </si>
+  <si>
+    <t>One review cycle of each draft deliverable is included.</t>
+  </si>
+  <si>
+    <t>No site survey or any on-site work will be completed.</t>
+  </si>
+  <si>
+    <t>We have not allowed for updates to the modelling, multiple iterations of modelling or calculations should changes to the area available, the location of the reserves or changes to the lot layout be made.</t>
+  </si>
+  <si>
+    <t>Geotechnical investigations, seepage assessments, groundwater assessments and earthworks specifications are excluded.</t>
+  </si>
+  <si>
+    <t>Detailed design, IFC drawings, construction specifications and contract documentation are excluded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiDAR information of the site and surrounding catchment area, if required. We can acquire this for you at cost if required.  </t>
+  </si>
+  <si>
+    <t>CAD/GIS plans of the proposed development,  including proposed finished surface levels if available at this stage of the project. Preferably, all plans are georeferenced to the correct co-ordinate system and 3d information is provided in xyz/ascii format.</t>
   </si>
 </sst>
 </file>
@@ -170,8 +266,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,15 +605,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0944417-D2F2-4A3A-B616-F8FA47D36E5C}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -561,29 +661,81 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
       <c r="C9" t="s">
         <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -591,79 +743,428 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
       <c r="C15" t="s">
         <v>21</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
       <c r="C16" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
       <c r="C23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
       <c r="C24" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
       <c r="C28" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
       <c r="C33" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
       <c r="C34" t="s">
         <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" t="s">
+        <v>51</v>
+      </c>
+      <c r="F36" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" t="s">
+        <v>53</v>
+      </c>
+      <c r="F38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G38" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" t="s">
+        <v>54</v>
+      </c>
+      <c r="G39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" t="s">
+        <v>55</v>
+      </c>
+      <c r="G40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" t="s">
+        <v>56</v>
+      </c>
+      <c r="F41" t="s">
+        <v>56</v>
+      </c>
+      <c r="G41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" t="s">
+        <v>57</v>
+      </c>
+      <c r="G42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" t="s">
+        <v>60</v>
+      </c>
+      <c r="F45" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" t="s">
+        <v>61</v>
+      </c>
+      <c r="F46" t="s">
+        <v>61</v>
+      </c>
+      <c r="G46" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
